--- a/public/exports-from-60-with-coowners/29189846.xlsx
+++ b/public/exports-from-60-with-coowners/29189846.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -14539,12 +14539,12 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279891</t>
+          <t xml:space="preserve">311279903</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279890</t>
+          <t xml:space="preserve">311279903</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282669</t>
+          <t xml:space="preserve">311372348</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -32689,7 +32689,7 @@
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290524</t>
+          <t xml:space="preserve">311373102</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
@@ -32989,12 +32989,12 @@
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369509</t>
+          <t xml:space="preserve">311374076</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M440" t="inlineStr">
@@ -36289,12 +36289,12 @@
       </c>
       <c r="K484" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290661</t>
+          <t xml:space="preserve">311290663</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M484" t="inlineStr">
@@ -36364,7 +36364,7 @@
       </c>
       <c r="K485" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290666</t>
+          <t xml:space="preserve">311374773</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
@@ -39364,12 +39364,12 @@
       </c>
       <c r="K525" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291095</t>
+          <t xml:space="preserve">311373742</t>
         </is>
       </c>
       <c r="L525" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M525" t="inlineStr">
@@ -40039,12 +40039,12 @@
       </c>
       <c r="K534" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293774</t>
+          <t xml:space="preserve">311373757</t>
         </is>
       </c>
       <c r="L534" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M534" t="inlineStr">
@@ -40264,7 +40264,7 @@
       </c>
       <c r="K537" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293846</t>
+          <t xml:space="preserve">311293847</t>
         </is>
       </c>
       <c r="L537" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189846.xlsx
+++ b/public/exports-from-60-with-coowners/29189846.xlsx
@@ -18364,7 +18364,7 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311284535</t>
+          <t xml:space="preserve">311368606</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -32689,7 +32689,7 @@
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373102</t>
+          <t xml:space="preserve">311290524</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189846.xlsx
+++ b/public/exports-from-60-with-coowners/29189846.xlsx
@@ -14539,12 +14539,12 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279903</t>
+          <t xml:space="preserve">311279891</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279903</t>
+          <t xml:space="preserve">311279890</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372348</t>
+          <t xml:space="preserve">311282669</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -18364,7 +18364,7 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368606</t>
+          <t xml:space="preserve">311284535</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -32989,12 +32989,12 @@
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374076</t>
+          <t xml:space="preserve">311369509</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M440" t="inlineStr">
@@ -36289,12 +36289,12 @@
       </c>
       <c r="K484" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290663</t>
+          <t xml:space="preserve">311290661</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M484" t="inlineStr">
@@ -36364,7 +36364,7 @@
       </c>
       <c r="K485" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374773</t>
+          <t xml:space="preserve">311290666</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
@@ -37166,7 +37166,7 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stænderpladsen 2</t>
+          <t xml:space="preserve">Tapdrupvej 100</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
@@ -37176,20 +37176,20 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t xml:space="preserve">9431029</t>
+          <t xml:space="preserve">3454867</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J496">
-        <v>1500</v>
+        <v>172</v>
       </c>
       <c r="K496" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368829</t>
+          <t xml:space="preserve">311375099</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
@@ -37256,15 +37256,15 @@
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J497">
-        <v>172</v>
+        <v>488</v>
       </c>
       <c r="K497" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375099</t>
+          <t xml:space="preserve">311375102</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
@@ -37331,15 +37331,15 @@
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J498">
-        <v>488</v>
+        <v>284</v>
       </c>
       <c r="K498" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375102</t>
+          <t xml:space="preserve">311375108</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
@@ -37391,7 +37391,7 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tapdrupvej 100</t>
+          <t xml:space="preserve">Tapdrupvej 100A</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
@@ -37406,15 +37406,15 @@
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J499">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="K499" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375108</t>
+          <t xml:space="preserve">311368613</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
@@ -37466,7 +37466,7 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tapdrupvej 100A</t>
+          <t xml:space="preserve">Tingvej 17</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
@@ -37476,20 +37476,20 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t xml:space="preserve">3454867</t>
+          <t xml:space="preserve">5589413</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="J500">
-        <v>273</v>
+        <v>1281</v>
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368613</t>
+          <t xml:space="preserve">311375539</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
@@ -37541,7 +37541,7 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvej 17</t>
+          <t xml:space="preserve">Tingvej 5</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
@@ -37551,20 +37551,20 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t xml:space="preserve">5589413</t>
+          <t xml:space="preserve">5591355</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J501">
-        <v>1281</v>
+        <v>3916</v>
       </c>
       <c r="K501" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375539</t>
+          <t xml:space="preserve">311375512</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
@@ -37616,7 +37616,7 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvej 5</t>
+          <t xml:space="preserve">Vinkelvej 172</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
@@ -37626,20 +37626,20 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t xml:space="preserve">5591355</t>
+          <t xml:space="preserve">4012634</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J502">
-        <v>3916</v>
+        <v>387</v>
       </c>
       <c r="K502" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375512</t>
+          <t xml:space="preserve">311375598</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
@@ -37691,7 +37691,7 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinkelvej 172</t>
+          <t xml:space="preserve">Vinkelvej 18A</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
@@ -37701,7 +37701,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t xml:space="preserve">4012634</t>
+          <t xml:space="preserve">8838279</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -37710,11 +37710,11 @@
         </is>
       </c>
       <c r="J503">
-        <v>387</v>
+        <v>284</v>
       </c>
       <c r="K503" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375598</t>
+          <t xml:space="preserve">311290692</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
@@ -37766,17 +37766,17 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinkelvej 18A</t>
+          <t xml:space="preserve">Vorningvej 33</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8830</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t xml:space="preserve">8838279</t>
+          <t xml:space="preserve">3468562</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -37785,11 +37785,11 @@
         </is>
       </c>
       <c r="J504">
-        <v>284</v>
+        <v>5165</v>
       </c>
       <c r="K504" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290692</t>
+          <t xml:space="preserve">311375628</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
@@ -37841,7 +37841,7 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vorningvej 33</t>
+          <t xml:space="preserve">Vorningvej 33A</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
@@ -37856,15 +37856,15 @@
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J505">
-        <v>5165</v>
+        <v>813</v>
       </c>
       <c r="K505" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375628</t>
+          <t xml:space="preserve">311290695</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
@@ -37916,30 +37916,30 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vorningvej 33A</t>
+          <t xml:space="preserve">Ådalshøjen 2</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t xml:space="preserve">8830</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t xml:space="preserve">3468562</t>
+          <t xml:space="preserve">8074164</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J506">
-        <v>813</v>
+        <v>722</v>
       </c>
       <c r="K506" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290695</t>
+          <t xml:space="preserve">311375648</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
@@ -37991,30 +37991,30 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalshøjen 2</t>
+          <t xml:space="preserve">Skolen 1</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">7470</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t xml:space="preserve">8074164</t>
+          <t xml:space="preserve">9214926</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J507">
-        <v>722</v>
+        <v>225</v>
       </c>
       <c r="K507" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375648</t>
+          <t xml:space="preserve">311372662</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
@@ -38024,7 +38024,7 @@
       </c>
       <c r="M507" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-28</t>
+          <t xml:space="preserve">2027-12-29</t>
         </is>
       </c>
       <c r="N507" t="inlineStr">
@@ -38066,7 +38066,7 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolen 1</t>
+          <t xml:space="preserve">Skolen 3</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
@@ -38081,15 +38081,15 @@
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J508">
-        <v>225</v>
+        <v>2661</v>
       </c>
       <c r="K508" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372662</t>
+          <t xml:space="preserve">311372723</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
@@ -38156,11 +38156,11 @@
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J509">
-        <v>2661</v>
+        <v>190</v>
       </c>
       <c r="K509" t="inlineStr">
         <is>
@@ -38231,11 +38231,11 @@
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J510">
-        <v>190</v>
+        <v>1945</v>
       </c>
       <c r="K510" t="inlineStr">
         <is>
@@ -38306,11 +38306,11 @@
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J511">
-        <v>1945</v>
+        <v>422</v>
       </c>
       <c r="K511" t="inlineStr">
         <is>
@@ -38381,11 +38381,11 @@
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J512">
-        <v>422</v>
+        <v>1025</v>
       </c>
       <c r="K512" t="inlineStr">
         <is>
@@ -38456,11 +38456,11 @@
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J513">
-        <v>1025</v>
+        <v>898</v>
       </c>
       <c r="K513" t="inlineStr">
         <is>
@@ -38516,30 +38516,30 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolen 3</t>
+          <t xml:space="preserve">Egeskovvej 75</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t xml:space="preserve">7470</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t xml:space="preserve">9214926</t>
+          <t xml:space="preserve">3451289</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J514">
-        <v>898</v>
+        <v>1067</v>
       </c>
       <c r="K514" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372723</t>
+          <t xml:space="preserve">311290810</t>
         </is>
       </c>
       <c r="L514" t="inlineStr">
@@ -38549,7 +38549,7 @@
       </c>
       <c r="M514" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-29</t>
+          <t xml:space="preserve">2027-12-30</t>
         </is>
       </c>
       <c r="N514" t="inlineStr">
@@ -38606,11 +38606,11 @@
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J515">
-        <v>1067</v>
+        <v>444</v>
       </c>
       <c r="K515" t="inlineStr">
         <is>
@@ -38681,11 +38681,11 @@
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J516">
-        <v>444</v>
+        <v>976</v>
       </c>
       <c r="K516" t="inlineStr">
         <is>
@@ -38756,11 +38756,11 @@
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J517">
-        <v>976</v>
+        <v>1673</v>
       </c>
       <c r="K517" t="inlineStr">
         <is>
@@ -38831,11 +38831,11 @@
       </c>
       <c r="I518" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J518">
-        <v>1673</v>
+        <v>3803</v>
       </c>
       <c r="K518" t="inlineStr">
         <is>
@@ -38906,11 +38906,11 @@
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J519">
-        <v>3803</v>
+        <v>380</v>
       </c>
       <c r="K519" t="inlineStr">
         <is>
@@ -38981,15 +38981,15 @@
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J520">
-        <v>380</v>
+        <v>306</v>
       </c>
       <c r="K520" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290810</t>
+          <t xml:space="preserve">311290811</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
@@ -39041,7 +39041,7 @@
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egeskovvej 75</t>
+          <t xml:space="preserve">Egeskovvej 4</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
@@ -39051,20 +39051,20 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t xml:space="preserve">3451289</t>
+          <t xml:space="preserve">8371196</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="J521">
-        <v>306</v>
+        <v>275</v>
       </c>
       <c r="K521" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290811</t>
+          <t xml:space="preserve">311291090</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
@@ -39074,7 +39074,7 @@
       </c>
       <c r="M521" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-30</t>
+          <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
       <c r="N521" t="inlineStr">
@@ -39116,7 +39116,7 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egeskovvej 4</t>
+          <t xml:space="preserve">Egeskovvej 4A</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
@@ -39131,15 +39131,15 @@
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="J522">
-        <v>275</v>
+        <v>172</v>
       </c>
       <c r="K522" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291090</t>
+          <t xml:space="preserve">311291089</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
@@ -39191,35 +39191,35 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egeskovvej 4A</t>
+          <t xml:space="preserve">Gl. Banevej 8</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">7470</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t xml:space="preserve">8371196</t>
+          <t xml:space="preserve">379840, 379841</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J523">
-        <v>172</v>
+        <v>3301</v>
       </c>
       <c r="K523" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291089</t>
+          <t xml:space="preserve">311291149</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M523" t="inlineStr">
@@ -39266,17 +39266,17 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Banevej 8</t>
+          <t xml:space="preserve">Kærsangervej 252</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t xml:space="preserve">7470</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t xml:space="preserve">379840, 379841</t>
+          <t xml:space="preserve">7715426</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -39285,11 +39285,11 @@
         </is>
       </c>
       <c r="J524">
-        <v>3301</v>
+        <v>635</v>
       </c>
       <c r="K524" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291149</t>
+          <t xml:space="preserve">311291095</t>
         </is>
       </c>
       <c r="L524" t="inlineStr">
@@ -39356,20 +39356,20 @@
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J525">
-        <v>635</v>
+        <v>101</v>
       </c>
       <c r="K525" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373742</t>
+          <t xml:space="preserve">311291095</t>
         </is>
       </c>
       <c r="L525" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M525" t="inlineStr">
@@ -39416,7 +39416,7 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærsangervej 252</t>
+          <t xml:space="preserve">Safranvej 10A</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
@@ -39426,25 +39426,25 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t xml:space="preserve">7715426</t>
+          <t xml:space="preserve">9254134</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J526">
-        <v>101</v>
+        <v>267</v>
       </c>
       <c r="K526" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291095</t>
+          <t xml:space="preserve">311291091</t>
         </is>
       </c>
       <c r="L526" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M526" t="inlineStr">
@@ -39491,7 +39491,7 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t xml:space="preserve">Safranvej 10A</t>
+          <t xml:space="preserve">Safranvej 8A</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
@@ -39506,15 +39506,15 @@
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J527">
-        <v>267</v>
+        <v>87</v>
       </c>
       <c r="K527" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291091</t>
+          <t xml:space="preserve">311291092</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
@@ -39566,7 +39566,7 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t xml:space="preserve">Safranvej 8A</t>
+          <t xml:space="preserve">Sct. Laurentii Vej 14C</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
@@ -39576,25 +39576,25 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t xml:space="preserve">9254134</t>
+          <t xml:space="preserve">5591308</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J528">
-        <v>87</v>
+        <v>384</v>
       </c>
       <c r="K528" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291092</t>
+          <t xml:space="preserve">311372532</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M528" t="inlineStr">
@@ -39641,35 +39641,35 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sct. Laurentii Vej 14C</t>
+          <t xml:space="preserve">Tjele Møllevej 10</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8830</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t xml:space="preserve">5591308</t>
+          <t xml:space="preserve">3455227</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J529">
-        <v>384</v>
+        <v>2628</v>
       </c>
       <c r="K529" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372532</t>
+          <t xml:space="preserve">311291101</t>
         </is>
       </c>
       <c r="L529" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M529" t="inlineStr">
@@ -39716,17 +39716,17 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjele Møllevej 10</t>
+          <t xml:space="preserve">Guldblommevej 14</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t xml:space="preserve">8830</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t xml:space="preserve">3455227</t>
+          <t xml:space="preserve">5587531</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -39735,11 +39735,11 @@
         </is>
       </c>
       <c r="J530">
-        <v>2628</v>
+        <v>836</v>
       </c>
       <c r="K530" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291101</t>
+          <t xml:space="preserve">311293801</t>
         </is>
       </c>
       <c r="L530" t="inlineStr">
@@ -39749,7 +39749,7 @@
       </c>
       <c r="M530" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-04</t>
+          <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
       <c r="N530" t="inlineStr">
@@ -39791,7 +39791,7 @@
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guldblommevej 14</t>
+          <t xml:space="preserve">Guldblommevej 16</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
@@ -39806,7 +39806,7 @@
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J531">
@@ -39814,7 +39814,7 @@
       </c>
       <c r="K531" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293801</t>
+          <t xml:space="preserve">311293850</t>
         </is>
       </c>
       <c r="L531" t="inlineStr">
@@ -39866,7 +39866,7 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guldblommevej 16</t>
+          <t xml:space="preserve">Kjeldvej 9</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
@@ -39876,20 +39876,20 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t xml:space="preserve">5587531</t>
+          <t xml:space="preserve">9050255</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J532">
-        <v>836</v>
+        <v>157</v>
       </c>
       <c r="K532" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293850</t>
+          <t xml:space="preserve">311293811</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
@@ -39941,7 +39941,7 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjeldvej 9</t>
+          <t xml:space="preserve">Liseborg Hegn 10A</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
@@ -39951,7 +39951,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t xml:space="preserve">9050255</t>
+          <t xml:space="preserve">10227103</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -39960,16 +39960,16 @@
         </is>
       </c>
       <c r="J533">
-        <v>157</v>
+        <v>6616</v>
       </c>
       <c r="K533" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293811</t>
+          <t xml:space="preserve">311293774</t>
         </is>
       </c>
       <c r="L533" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M533" t="inlineStr">
@@ -40016,7 +40016,7 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liseborg Hegn 10A</t>
+          <t xml:space="preserve">Ll. Sct. Hans Gade 7</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
@@ -40026,20 +40026,20 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t xml:space="preserve">10227103</t>
+          <t xml:space="preserve">100002554</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J534">
-        <v>6616</v>
+        <v>464</v>
       </c>
       <c r="K534" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373757</t>
+          <t xml:space="preserve">311373762</t>
         </is>
       </c>
       <c r="L534" t="inlineStr">
@@ -40091,7 +40091,7 @@
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ll. Sct. Hans Gade 7</t>
+          <t xml:space="preserve">Ll. Sct. Hans Gade 9</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
@@ -40106,11 +40106,11 @@
       </c>
       <c r="I535" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J535">
-        <v>464</v>
+        <v>1037</v>
       </c>
       <c r="K535" t="inlineStr">
         <is>
@@ -40166,7 +40166,7 @@
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ll. Sct. Hans Gade 9</t>
+          <t xml:space="preserve">Merkurvej 71</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
@@ -40176,7 +40176,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t xml:space="preserve">100002554</t>
+          <t xml:space="preserve">3449917</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -40185,11 +40185,11 @@
         </is>
       </c>
       <c r="J536">
-        <v>1037</v>
+        <v>594</v>
       </c>
       <c r="K536" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373762</t>
+          <t xml:space="preserve">311293846</t>
         </is>
       </c>
       <c r="L536" t="inlineStr">
@@ -40241,7 +40241,7 @@
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t xml:space="preserve">Merkurvej 71</t>
+          <t xml:space="preserve">Rødevej 2A</t>
         </is>
       </c>
       <c r="G537" t="inlineStr">
@@ -40251,7 +40251,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t xml:space="preserve">3449917</t>
+          <t xml:space="preserve">8940099</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -40260,11 +40260,11 @@
         </is>
       </c>
       <c r="J537">
-        <v>594</v>
+        <v>1569</v>
       </c>
       <c r="K537" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293847</t>
+          <t xml:space="preserve">311374142</t>
         </is>
       </c>
       <c r="L537" t="inlineStr">
@@ -40316,7 +40316,7 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødevej 2A</t>
+          <t xml:space="preserve">Rødevej 2D</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
@@ -40331,15 +40331,15 @@
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J538">
-        <v>1569</v>
+        <v>150</v>
       </c>
       <c r="K538" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374142</t>
+          <t xml:space="preserve">311374136</t>
         </is>
       </c>
       <c r="L538" t="inlineStr">
@@ -40391,30 +40391,30 @@
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødevej 2D</t>
+          <t xml:space="preserve">Skolegade 27</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">9632</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940099</t>
+          <t xml:space="preserve">3464052</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J539">
-        <v>150</v>
+        <v>2918</v>
       </c>
       <c r="K539" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374136</t>
+          <t xml:space="preserve">311372613</t>
         </is>
       </c>
       <c r="L539" t="inlineStr">
@@ -40481,15 +40481,15 @@
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J540">
-        <v>2918</v>
+        <v>156</v>
       </c>
       <c r="K540" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372613</t>
+          <t xml:space="preserve">311374194</t>
         </is>
       </c>
       <c r="L540" t="inlineStr">
@@ -40556,15 +40556,15 @@
       </c>
       <c r="I541" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J541">
-        <v>156</v>
+        <v>294</v>
       </c>
       <c r="K541" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374194</t>
+          <t xml:space="preserve">311374196</t>
         </is>
       </c>
       <c r="L541" t="inlineStr">
@@ -40631,15 +40631,15 @@
       </c>
       <c r="I542" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J542">
-        <v>294</v>
+        <v>178</v>
       </c>
       <c r="K542" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374196</t>
+          <t xml:space="preserve">311293836</t>
         </is>
       </c>
       <c r="L542" t="inlineStr">
@@ -40706,15 +40706,15 @@
       </c>
       <c r="I543" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J543">
-        <v>178</v>
+        <v>2275</v>
       </c>
       <c r="K543" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293836</t>
+          <t xml:space="preserve">311293831</t>
         </is>
       </c>
       <c r="L543" t="inlineStr">
@@ -40781,15 +40781,15 @@
       </c>
       <c r="I544" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J544">
-        <v>2275</v>
+        <v>333</v>
       </c>
       <c r="K544" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293831</t>
+          <t xml:space="preserve">311293833</t>
         </is>
       </c>
       <c r="L544" t="inlineStr">
@@ -40841,7 +40841,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 27</t>
+          <t xml:space="preserve">Skolegade 29</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
@@ -40856,15 +40856,15 @@
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J545">
-        <v>333</v>
+        <v>297</v>
       </c>
       <c r="K545" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293833</t>
+          <t xml:space="preserve">311374191</t>
         </is>
       </c>
       <c r="L545" t="inlineStr">
@@ -40901,12 +40901,12 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viborg Kommune</t>
+          <t xml:space="preserve">Boligselskabet Sct. Jørgen, Viborg</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -40916,30 +40916,30 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 29</t>
+          <t xml:space="preserve">Videbechs Alle 165A</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t xml:space="preserve">9632</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t xml:space="preserve">3464052</t>
+          <t xml:space="preserve">383686, 383688, 383687, 383689</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="J546">
-        <v>297</v>
+        <v>734</v>
       </c>
       <c r="K546" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374191</t>
+          <t xml:space="preserve">311375579</t>
         </is>
       </c>
       <c r="L546" t="inlineStr">
@@ -40976,12 +40976,12 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boligselskabet Sct. Jørgen, Viborg</t>
+          <t xml:space="preserve">Viborg Kommune</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -40991,7 +40991,7 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t xml:space="preserve">Videbechs Alle 165A</t>
+          <t xml:space="preserve">Liseborgvej 35A</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
@@ -41001,30 +41001,30 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t xml:space="preserve">383686, 383688, 383687, 383689</t>
+          <t xml:space="preserve">1508276, 100535682</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J547">
-        <v>734</v>
+        <v>854</v>
       </c>
       <c r="K547" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375579</t>
+          <t xml:space="preserve">311373759</t>
         </is>
       </c>
       <c r="L547" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M547" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-22</t>
+          <t xml:space="preserve">2028-02-15</t>
         </is>
       </c>
       <c r="N547" t="inlineStr">
@@ -41066,40 +41066,40 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liseborgvej 35A</t>
+          <t xml:space="preserve">Brandstrupvej 27</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8840</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t xml:space="preserve">1508276, 100535682</t>
+          <t xml:space="preserve">4011561</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J548">
-        <v>854</v>
+        <v>1178</v>
       </c>
       <c r="K548" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373759</t>
+          <t xml:space="preserve">311369993</t>
         </is>
       </c>
       <c r="L548" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Dansk Energisyn</t>
         </is>
       </c>
       <c r="M548" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-15</t>
+          <t xml:space="preserve">2029-04-09</t>
         </is>
       </c>
       <c r="N548" t="inlineStr">
@@ -41126,12 +41126,12 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viborg Kommune</t>
+          <t xml:space="preserve">Mercantec</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -41141,40 +41141,40 @@
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brandstrupvej 27</t>
+          <t xml:space="preserve">Banegårds Alle 1</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t xml:space="preserve">8840</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t xml:space="preserve">4011561</t>
+          <t xml:space="preserve">430971, 430972</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J549">
-        <v>1178</v>
+        <v>15028</v>
       </c>
       <c r="K549" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369993</t>
+          <t xml:space="preserve">311431225</t>
         </is>
       </c>
       <c r="L549" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Energisyn</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M549" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-09</t>
+          <t xml:space="preserve">2030-04-01</t>
         </is>
       </c>
       <c r="N549" t="inlineStr">
@@ -41201,12 +41201,12 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercantec</t>
+          <t xml:space="preserve">Viborg Kommune</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
@@ -41216,7 +41216,7 @@
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banegårds Alle 1</t>
+          <t xml:space="preserve">Guldbækvej 11</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
@@ -41226,7 +41226,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t xml:space="preserve">430971, 430972</t>
+          <t xml:space="preserve">5593617</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -41235,21 +41235,21 @@
         </is>
       </c>
       <c r="J550">
-        <v>15028</v>
+        <v>177</v>
       </c>
       <c r="K550" t="inlineStr">
         <is>
-          <t xml:space="preserve">311431225</t>
+          <t xml:space="preserve">311445381</t>
         </is>
       </c>
       <c r="L550" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M550" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-04-01</t>
+          <t xml:space="preserve">2030-06-23</t>
         </is>
       </c>
       <c r="N550" t="inlineStr">
@@ -41291,40 +41291,40 @@
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guldbækvej 11</t>
+          <t xml:space="preserve">Stadionvej 6A</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8832</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t xml:space="preserve">5593617</t>
+          <t xml:space="preserve">3464853</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J551">
-        <v>177</v>
+        <v>335</v>
       </c>
       <c r="K551" t="inlineStr">
         <is>
-          <t xml:space="preserve">311445381</t>
+          <t xml:space="preserve">311467972</t>
         </is>
       </c>
       <c r="L551" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
         </is>
       </c>
       <c r="M551" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-23</t>
+          <t xml:space="preserve">2030-10-19</t>
         </is>
       </c>
       <c r="N551" t="inlineStr">
@@ -41351,12 +41351,12 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viborg Kommune</t>
+          <t xml:space="preserve">ABF Torvegadecentret</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -41366,40 +41366,40 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 6A</t>
+          <t xml:space="preserve">Torvegade 10A</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t xml:space="preserve">8832</t>
+          <t xml:space="preserve">8850</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t xml:space="preserve">3464853</t>
+          <t xml:space="preserve">379369, 379370, 379371, 379372, 379373, 379374</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J552">
-        <v>335</v>
+        <v>3439</v>
       </c>
       <c r="K552" t="inlineStr">
         <is>
-          <t xml:space="preserve">311467972</t>
+          <t xml:space="preserve">311474838</t>
         </is>
       </c>
       <c r="L552" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M552" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-19</t>
+          <t xml:space="preserve">2030-11-11</t>
         </is>
       </c>
       <c r="N552" t="inlineStr">
@@ -41426,12 +41426,12 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABF Torvegadecentret</t>
+          <t xml:space="preserve">Viborg Kommune</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
@@ -41441,40 +41441,40 @@
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvegade 10A</t>
+          <t xml:space="preserve">Rørsangervej 5</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t xml:space="preserve">8850</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t xml:space="preserve">379369, 379370, 379371, 379372, 379373, 379374</t>
+          <t xml:space="preserve">5586340</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J553">
-        <v>3439</v>
+        <v>313</v>
       </c>
       <c r="K553" t="inlineStr">
         <is>
-          <t xml:space="preserve">311474838</t>
+          <t xml:space="preserve">311476458</t>
         </is>
       </c>
       <c r="L553" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Ydes Bygningsrådgivning</t>
         </is>
       </c>
       <c r="M553" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-11</t>
+          <t xml:space="preserve">2030-11-17</t>
         </is>
       </c>
       <c r="N553" t="inlineStr">
@@ -41516,7 +41516,7 @@
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rørsangervej 5</t>
+          <t xml:space="preserve">Søakset 2</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
@@ -41526,30 +41526,30 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t xml:space="preserve">5586340</t>
+          <t xml:space="preserve">100124844</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J554">
-        <v>313</v>
+        <v>1565</v>
       </c>
       <c r="K554" t="inlineStr">
         <is>
-          <t xml:space="preserve">311476458</t>
+          <t xml:space="preserve">311505527</t>
         </is>
       </c>
       <c r="L554" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ydes Bygningsrådgivning</t>
+          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
         </is>
       </c>
       <c r="M554" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-17</t>
+          <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
       <c r="N554" t="inlineStr">
@@ -41591,40 +41591,40 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søakset 2</t>
+          <t xml:space="preserve">Naundrupvej 7A</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">9632</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t xml:space="preserve">100124844</t>
+          <t xml:space="preserve">749066, 3456742</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J555">
-        <v>1565</v>
+        <v>348</v>
       </c>
       <c r="K555" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505527</t>
+          <t xml:space="preserve">311540479</t>
         </is>
       </c>
       <c r="L555" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M555" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-22</t>
+          <t xml:space="preserve">2031-08-12</t>
         </is>
       </c>
       <c r="N555" t="inlineStr">
@@ -41651,12 +41651,12 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viborg Kommune</t>
+          <t xml:space="preserve">Boligselskabet Sct. Jørgen, Viborg</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
@@ -41666,40 +41666,40 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naundrupvej 7A</t>
+          <t xml:space="preserve">Marsk Stigs Vej 4</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t xml:space="preserve">9632</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t xml:space="preserve">749066, 3456742</t>
+          <t xml:space="preserve">421278, 421279, 421280</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J556">
-        <v>348</v>
+        <v>9880</v>
       </c>
       <c r="K556" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540479</t>
+          <t xml:space="preserve">311599601</t>
         </is>
       </c>
       <c r="L556" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Sweco Danmark A/S - LBF</t>
         </is>
       </c>
       <c r="M556" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-12</t>
+          <t xml:space="preserve">2032-05-11</t>
         </is>
       </c>
       <c r="N556" t="inlineStr">
@@ -41726,12 +41726,12 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boligselskabet Sct. Jørgen, Viborg</t>
+          <t xml:space="preserve">Viborg Kommune</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
@@ -41741,30 +41741,30 @@
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marsk Stigs Vej 4</t>
+          <t xml:space="preserve">Anlægsgade 2</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">7850</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t xml:space="preserve">421278, 421279, 421280</t>
+          <t xml:space="preserve">384187, 384188</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J557">
-        <v>9880</v>
+        <v>3245</v>
       </c>
       <c r="K557" t="inlineStr">
         <is>
-          <t xml:space="preserve">311599601</t>
+          <t xml:space="preserve">311619862</t>
         </is>
       </c>
       <c r="L557" t="inlineStr">
@@ -41774,7 +41774,7 @@
       </c>
       <c r="M557" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-11</t>
+          <t xml:space="preserve">2032-08-11</t>
         </is>
       </c>
       <c r="N557" t="inlineStr">
@@ -41801,12 +41801,12 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viborg Kommune</t>
+          <t xml:space="preserve">Professionshøjskolen VIA University College</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
@@ -41816,17 +41816,17 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anlægsgade 2</t>
+          <t xml:space="preserve">Prinsens Alle 2</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t xml:space="preserve">7850</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t xml:space="preserve">384187, 384188</t>
+          <t xml:space="preserve">382460, 382461</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -41835,21 +41835,21 @@
         </is>
       </c>
       <c r="J558">
-        <v>3245</v>
+        <v>20359</v>
       </c>
       <c r="K558" t="inlineStr">
         <is>
-          <t xml:space="preserve">311619862</t>
+          <t xml:space="preserve">311622987</t>
         </is>
       </c>
       <c r="L558" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S - LBF</t>
+          <t xml:space="preserve">Norconsult A/S</t>
         </is>
       </c>
       <c r="M558" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-11</t>
+          <t xml:space="preserve">2032-08-25</t>
         </is>
       </c>
       <c r="N558" t="inlineStr">
@@ -41876,12 +41876,12 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professionshøjskolen VIA University College</t>
+          <t xml:space="preserve">Viborg Kommune</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
@@ -41891,7 +41891,7 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prinsens Alle 2</t>
+          <t xml:space="preserve">Tingvej 20</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
@@ -41901,7 +41901,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t xml:space="preserve">382460, 382461</t>
+          <t xml:space="preserve">5589417</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -41910,11 +41910,11 @@
         </is>
       </c>
       <c r="J559">
-        <v>20359</v>
+        <v>8141</v>
       </c>
       <c r="K559" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622987</t>
+          <t xml:space="preserve">311652390</t>
         </is>
       </c>
       <c r="L559" t="inlineStr">
@@ -41924,7 +41924,7 @@
       </c>
       <c r="M559" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-25</t>
+          <t xml:space="preserve">2033-01-04</t>
         </is>
       </c>
       <c r="N559" t="inlineStr">
@@ -41966,7 +41966,7 @@
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvej 20</t>
+          <t xml:space="preserve">H.C. Andersens Vej 5</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
@@ -41976,30 +41976,30 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t xml:space="preserve">5589417</t>
+          <t xml:space="preserve">5590613</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J560">
-        <v>8141</v>
+        <v>478</v>
       </c>
       <c r="K560" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652390</t>
+          <t xml:space="preserve">311659256</t>
         </is>
       </c>
       <c r="L560" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norconsult A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M560" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-04</t>
+          <t xml:space="preserve">2033-02-09</t>
         </is>
       </c>
       <c r="N560" t="inlineStr">
@@ -42041,7 +42041,7 @@
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t xml:space="preserve">H.C. Andersens Vej 5</t>
+          <t xml:space="preserve">Rørsangervej 5</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
@@ -42051,30 +42051,30 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t xml:space="preserve">5590613</t>
+          <t xml:space="preserve">5586340</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J561">
-        <v>478</v>
+        <v>357</v>
       </c>
       <c r="K561" t="inlineStr">
         <is>
-          <t xml:space="preserve">311659256</t>
+          <t xml:space="preserve">311661783</t>
         </is>
       </c>
       <c r="L561" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
         </is>
       </c>
       <c r="M561" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-09</t>
+          <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
       <c r="N561" t="inlineStr">
@@ -42116,40 +42116,40 @@
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rørsangervej 5</t>
+          <t xml:space="preserve">Stadionvej 18</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">7850</t>
         </is>
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t xml:space="preserve">5586340</t>
+          <t xml:space="preserve">384189, 384190</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J562">
-        <v>357</v>
+        <v>137</v>
       </c>
       <c r="K562" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661783</t>
+          <t xml:space="preserve">311683914</t>
         </is>
       </c>
       <c r="L562" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+          <t xml:space="preserve">Sweco Danmark A/S - LBF</t>
         </is>
       </c>
       <c r="M562" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-22</t>
+          <t xml:space="preserve">2033-05-30</t>
         </is>
       </c>
       <c r="N562" t="inlineStr">
@@ -42176,12 +42176,12 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viborg Kommune</t>
+          <t xml:space="preserve">Boligselskabet Sct. Jørgen, Viborg</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
@@ -42191,30 +42191,30 @@
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 18</t>
+          <t xml:space="preserve">Blichersvænge 1</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t xml:space="preserve">7850</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t xml:space="preserve">384189, 384190</t>
+          <t xml:space="preserve">100178735, 100178736</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J563">
-        <v>137</v>
+        <v>872</v>
       </c>
       <c r="K563" t="inlineStr">
         <is>
-          <t xml:space="preserve">311683914</t>
+          <t xml:space="preserve">311685873</t>
         </is>
       </c>
       <c r="L563" t="inlineStr">
@@ -42224,7 +42224,7 @@
       </c>
       <c r="M563" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-30</t>
+          <t xml:space="preserve">2033-06-06</t>
         </is>
       </c>
       <c r="N563" t="inlineStr">
@@ -42266,30 +42266,30 @@
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blichersvænge 1</t>
+          <t xml:space="preserve">Nørregade 3</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8830</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t xml:space="preserve">100178735, 100178736</t>
+          <t xml:space="preserve">384199, 384200</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J564">
-        <v>872</v>
+        <v>2115</v>
       </c>
       <c r="K564" t="inlineStr">
         <is>
-          <t xml:space="preserve">311685873</t>
+          <t xml:space="preserve">311685866</t>
         </is>
       </c>
       <c r="L564" t="inlineStr">
@@ -42326,12 +42326,12 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boligselskabet Sct. Jørgen, Viborg</t>
+          <t xml:space="preserve">Viborg Kommune</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
@@ -42341,17 +42341,17 @@
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 3</t>
+          <t xml:space="preserve">Banegårdspladsen 4</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t xml:space="preserve">8830</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t xml:space="preserve">384199, 384200</t>
+          <t xml:space="preserve">381021, 381022, 381023, 381024, 381025</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -42360,11 +42360,11 @@
         </is>
       </c>
       <c r="J565">
-        <v>2115</v>
+        <v>1814</v>
       </c>
       <c r="K565" t="inlineStr">
         <is>
-          <t xml:space="preserve">311685866</t>
+          <t xml:space="preserve">311702960</t>
         </is>
       </c>
       <c r="L565" t="inlineStr">
@@ -42374,7 +42374,7 @@
       </c>
       <c r="M565" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-06</t>
+          <t xml:space="preserve">2033-08-27</t>
         </is>
       </c>
       <c r="N565" t="inlineStr">
@@ -42401,12 +42401,12 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viborg Kommune</t>
+          <t xml:space="preserve">BOLIGSELSKABET VIBORG</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
@@ -42416,7 +42416,7 @@
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banegårdspladsen 4</t>
+          <t xml:space="preserve">N.F.S. Grundtvigs Vej 13</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
@@ -42426,7 +42426,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t xml:space="preserve">381021, 381022, 381023, 381024, 381025</t>
+          <t xml:space="preserve">384785, 384786, 384787</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -42435,11 +42435,11 @@
         </is>
       </c>
       <c r="J566">
-        <v>1814</v>
+        <v>10635</v>
       </c>
       <c r="K566" t="inlineStr">
         <is>
-          <t xml:space="preserve">311702960</t>
+          <t xml:space="preserve">311757301</t>
         </is>
       </c>
       <c r="L566" t="inlineStr">
@@ -42449,7 +42449,7 @@
       </c>
       <c r="M566" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-27</t>
+          <t xml:space="preserve">2034-05-06</t>
         </is>
       </c>
       <c r="N566" t="inlineStr">
@@ -42491,7 +42491,7 @@
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t xml:space="preserve">N.F.S. Grundtvigs Vej 13</t>
+          <t xml:space="preserve">Odshøjvej 5A</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
@@ -42501,7 +42501,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t xml:space="preserve">384785, 384786, 384787</t>
+          <t xml:space="preserve">383742, 383743, 383744</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -42510,11 +42510,11 @@
         </is>
       </c>
       <c r="J567">
-        <v>10635</v>
+        <v>1930</v>
       </c>
       <c r="K567" t="inlineStr">
         <is>
-          <t xml:space="preserve">311757301</t>
+          <t xml:space="preserve">311757916</t>
         </is>
       </c>
       <c r="L567" t="inlineStr">
@@ -42524,7 +42524,7 @@
       </c>
       <c r="M567" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-06</t>
+          <t xml:space="preserve">2034-05-08</t>
         </is>
       </c>
       <c r="N567" t="inlineStr">
@@ -42551,12 +42551,12 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOLIGSELSKABET VIBORG</t>
+          <t xml:space="preserve">Viborg Kommune</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
@@ -42566,40 +42566,40 @@
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odshøjvej 5A</t>
+          <t xml:space="preserve">Jørgens Alle 42</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8850</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t xml:space="preserve">383742, 383743, 383744</t>
+          <t xml:space="preserve">7775696</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J568">
-        <v>1930</v>
+        <v>394</v>
       </c>
       <c r="K568" t="inlineStr">
         <is>
-          <t xml:space="preserve">311757916</t>
+          <t xml:space="preserve">311764588</t>
         </is>
       </c>
       <c r="L568" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S - LBF</t>
+          <t xml:space="preserve">Ydes Bygningsrådgivning</t>
         </is>
       </c>
       <c r="M568" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-08</t>
+          <t xml:space="preserve">2034-06-06</t>
         </is>
       </c>
       <c r="N568" t="inlineStr">
@@ -42641,40 +42641,40 @@
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jørgens Alle 42</t>
+          <t xml:space="preserve">Gl. Randersvej 35</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t xml:space="preserve">8850</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t xml:space="preserve">7775696</t>
+          <t xml:space="preserve">8837678</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J569">
-        <v>394</v>
+        <v>13000</v>
       </c>
       <c r="K569" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764588</t>
+          <t xml:space="preserve">311797218</t>
         </is>
       </c>
       <c r="L569" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ydes Bygningsrådgivning</t>
+          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
         </is>
       </c>
       <c r="M569" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-06</t>
+          <t xml:space="preserve">2034-11-13</t>
         </is>
       </c>
       <c r="N569" t="inlineStr">
@@ -42716,7 +42716,7 @@
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Randersvej 35</t>
+          <t xml:space="preserve">Rughavevej 66</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
@@ -42726,30 +42726,30 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t xml:space="preserve">8837678</t>
+          <t xml:space="preserve">5590174</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J570">
-        <v>13000</v>
+        <v>683</v>
       </c>
       <c r="K570" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797218</t>
+          <t xml:space="preserve">311805525</t>
         </is>
       </c>
       <c r="L570" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
         </is>
       </c>
       <c r="M570" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-13</t>
+          <t xml:space="preserve">2035-01-13</t>
         </is>
       </c>
       <c r="N570" t="inlineStr">
@@ -42791,7 +42791,7 @@
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rughavevej 66</t>
+          <t xml:space="preserve">Sct. Leonis Gade 8</t>
         </is>
       </c>
       <c r="G571" t="inlineStr">
@@ -42801,30 +42801,30 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t xml:space="preserve">5590174</t>
+          <t xml:space="preserve">5585392</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J571">
-        <v>683</v>
+        <v>310</v>
       </c>
       <c r="K571" t="inlineStr">
         <is>
-          <t xml:space="preserve">311805525</t>
+          <t xml:space="preserve">311858724</t>
         </is>
       </c>
       <c r="L571" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+          <t xml:space="preserve">Norconsult Danmark A/S</t>
         </is>
       </c>
       <c r="M571" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-01-13</t>
+          <t xml:space="preserve">2035-09-29</t>
         </is>
       </c>
       <c r="N571" t="inlineStr">
@@ -42866,17 +42866,17 @@
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sct. Leonis Gade 8</t>
+          <t xml:space="preserve">Iglsøvej 68B</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">7850</t>
         </is>
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t xml:space="preserve">5585392</t>
+          <t xml:space="preserve">4048544</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -42885,21 +42885,21 @@
         </is>
       </c>
       <c r="J572">
-        <v>310</v>
+        <v>515</v>
       </c>
       <c r="K572" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858724</t>
+          <t xml:space="preserve">311869171</t>
         </is>
       </c>
       <c r="L572" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norconsult Danmark A/S</t>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
         </is>
       </c>
       <c r="M572" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-29</t>
+          <t xml:space="preserve">2035-11-19</t>
         </is>
       </c>
       <c r="N572" t="inlineStr">
@@ -42926,12 +42926,12 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viborg Kommune</t>
+          <t xml:space="preserve">Viborg Idrætshøjskole S/I</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
@@ -42941,40 +42941,40 @@
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iglsøvej 68B</t>
+          <t xml:space="preserve">Vinkelvej 22A</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t xml:space="preserve">7850</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t xml:space="preserve">4048544</t>
+          <t xml:space="preserve">749139, 5594844</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="J573">
-        <v>515</v>
+        <v>348</v>
       </c>
       <c r="K573" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869171</t>
+          <t xml:space="preserve">311879358</t>
         </is>
       </c>
       <c r="L573" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M573" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-19</t>
+          <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
       <c r="N573" t="inlineStr">
@@ -43001,12 +43001,12 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viborg Idrætshøjskole S/I</t>
+          <t xml:space="preserve">Viborg Kommune</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
@@ -43016,7 +43016,7 @@
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinkelvej 22A</t>
+          <t xml:space="preserve">Martinesminde 2</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
@@ -43026,30 +43026,30 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t xml:space="preserve">749139, 5594844</t>
+          <t xml:space="preserve">100617942</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J574">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K574" t="inlineStr">
         <is>
-          <t xml:space="preserve">311879358</t>
+          <t xml:space="preserve">311881722</t>
         </is>
       </c>
       <c r="L574" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M574" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-29</t>
+          <t xml:space="preserve">2036-02-12</t>
         </is>
       </c>
       <c r="N574" t="inlineStr">
@@ -43091,7 +43091,7 @@
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martinesminde 2</t>
+          <t xml:space="preserve">Stænderpladsen 2</t>
         </is>
       </c>
       <c r="G575" t="inlineStr">
@@ -43101,30 +43101,30 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t xml:space="preserve">100617942</t>
+          <t xml:space="preserve">9431029</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J575">
-        <v>349</v>
+        <v>1500</v>
       </c>
       <c r="K575" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881722</t>
+          <t xml:space="preserve">311929568</t>
         </is>
       </c>
       <c r="L575" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M575" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-12</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N575" t="inlineStr">
